--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\DCPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FCF6BD3-5DBC-4B42-B14E-8401B091933E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F50171-036F-4D0A-97E3-8807B3774118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\DCPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7D81A26-4781-41B5-B653-2982B9C7F70E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2834711D-856D-49A3-814B-EA5FCEA47A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -823,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -11030,7 +11030,7 @@
       <c r="I378" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J378">
+      <c r="J378" s="2">
         <v>0</v>
       </c>
       <c r="K378" s="1">
@@ -49277,7 +49277,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\DCPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2834711D-856D-49A3-814B-EA5FCEA47A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{40499B96-1BE8-44FF-998D-1E2697F65C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -86,19 +86,19 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Winter Weather</t>
+    <t>Mark Complete</t>
   </si>
   <si>
-    <t>Drowsy Driving</t>
-  </si>
-  <si>
-    <t>Mark Complete</t>
+    <t>Winter Weather</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
   </si>
   <si>
     <t>Safe Lifting for Commercial Drivers</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
   </si>
   <si>
     <t>DCPS</t>
@@ -823,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -881,7 +881,7 @@
         <v>21</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>13</v>
@@ -910,7 +910,7 @@
         <v>22</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>13</v>
@@ -939,7 +939,7 @@
         <v>23</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>13</v>
@@ -968,7 +968,7 @@
         <v>24</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>13</v>
@@ -997,7 +997,7 @@
         <v>25</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>13</v>
@@ -1026,7 +1026,7 @@
         <v>26</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>13</v>
@@ -1055,7 +1055,7 @@
         <v>27</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>13</v>
@@ -1084,7 +1084,7 @@
         <v>28</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>13</v>
@@ -1113,7 +1113,7 @@
         <v>29</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>13</v>
@@ -1142,7 +1142,7 @@
         <v>30</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>13</v>
@@ -1171,7 +1171,7 @@
         <v>31</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>13</v>
@@ -1200,7 +1200,7 @@
         <v>32</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>13</v>
@@ -1229,7 +1229,7 @@
         <v>33</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>13</v>
@@ -1258,7 +1258,7 @@
         <v>34</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1287,7 +1287,7 @@
         <v>35</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>13</v>
@@ -1316,7 +1316,7 @@
         <v>36</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>13</v>
@@ -1345,7 +1345,7 @@
         <v>37</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>13</v>
@@ -1374,7 +1374,7 @@
         <v>38</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>13</v>
@@ -1403,7 +1403,7 @@
         <v>39</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>13</v>
@@ -1432,7 +1432,7 @@
         <v>40</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>14</v>
@@ -1456,7 +1456,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="1"/>
       <c r="M22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
@@ -1470,7 +1470,7 @@
         <v>41</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>13</v>
@@ -1499,7 +1499,7 @@
         <v>42</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>13</v>
@@ -1528,7 +1528,7 @@
         <v>43</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>10</v>
@@ -1557,7 +1557,7 @@
         <v>44</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>13</v>
@@ -1586,7 +1586,7 @@
         <v>45</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>13</v>
@@ -1615,7 +1615,7 @@
         <v>46</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>13</v>
@@ -1644,7 +1644,7 @@
         <v>47</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>13</v>
@@ -1673,7 +1673,7 @@
         <v>48</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>14</v>
@@ -1697,7 +1697,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="1"/>
       <c r="M31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
@@ -1711,7 +1711,7 @@
         <v>49</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>10</v>
@@ -1740,7 +1740,7 @@
         <v>50</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>13</v>
@@ -1769,7 +1769,7 @@
         <v>51</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>13</v>
@@ -1798,7 +1798,7 @@
         <v>52</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>10</v>
@@ -1827,7 +1827,7 @@
         <v>53</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>13</v>
@@ -1856,7 +1856,7 @@
         <v>54</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>10</v>
@@ -1885,7 +1885,7 @@
         <v>55</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>13</v>
@@ -1914,7 +1914,7 @@
         <v>56</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1943,7 +1943,7 @@
         <v>57</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>13</v>
@@ -1972,7 +1972,7 @@
         <v>58</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>13</v>
@@ -2001,7 +2001,7 @@
         <v>59</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>13</v>
@@ -2030,7 +2030,7 @@
         <v>60</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>13</v>
@@ -2059,7 +2059,7 @@
         <v>61</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>13</v>
@@ -2088,7 +2088,7 @@
         <v>62</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>13</v>
@@ -2117,7 +2117,7 @@
         <v>63</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>13</v>
@@ -2146,7 +2146,7 @@
         <v>64</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>13</v>
@@ -2175,7 +2175,7 @@
         <v>65</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>13</v>
@@ -2204,7 +2204,7 @@
         <v>66</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>13</v>
@@ -2233,7 +2233,7 @@
         <v>67</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>13</v>
@@ -2262,7 +2262,7 @@
         <v>68</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>13</v>
@@ -2291,7 +2291,7 @@
         <v>69</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>13</v>
@@ -2320,7 +2320,7 @@
         <v>70</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>12</v>
@@ -2344,7 +2344,7 @@
       <c r="J54" s="2"/>
       <c r="K54" s="1"/>
       <c r="M54" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
@@ -2358,7 +2358,7 @@
         <v>71</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2387,7 +2387,7 @@
         <v>72</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>13</v>
@@ -2416,7 +2416,7 @@
         <v>73</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>12</v>
@@ -2440,7 +2440,7 @@
       <c r="J58" s="2"/>
       <c r="K58" s="1"/>
       <c r="M58" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
@@ -2454,7 +2454,7 @@
         <v>74</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>13</v>
@@ -2483,7 +2483,7 @@
         <v>75</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>13</v>
@@ -2512,7 +2512,7 @@
         <v>76</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>13</v>
@@ -2541,7 +2541,7 @@
         <v>77</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>10</v>
@@ -2570,7 +2570,7 @@
         <v>78</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>13</v>
@@ -2599,7 +2599,7 @@
         <v>79</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>14</v>
@@ -2623,7 +2623,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="1"/>
       <c r="M65" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
@@ -2637,7 +2637,7 @@
         <v>80</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>13</v>
@@ -2666,7 +2666,7 @@
         <v>81</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>13</v>
@@ -2695,7 +2695,7 @@
         <v>82</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>13</v>
@@ -2724,7 +2724,7 @@
         <v>83</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>13</v>
@@ -2753,7 +2753,7 @@
         <v>84</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>13</v>
@@ -2782,7 +2782,7 @@
         <v>85</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>14</v>
@@ -2806,7 +2806,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="1"/>
       <c r="M72" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
@@ -2820,7 +2820,7 @@
         <v>86</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>12</v>
@@ -2844,7 +2844,7 @@
       <c r="J74" s="2"/>
       <c r="K74" s="1"/>
       <c r="M74" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
@@ -2858,7 +2858,7 @@
         <v>87</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>12</v>
@@ -2882,7 +2882,7 @@
       <c r="J76" s="2"/>
       <c r="K76" s="1"/>
       <c r="M76" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
@@ -2896,7 +2896,7 @@
         <v>88</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>13</v>
@@ -2925,7 +2925,7 @@
         <v>89</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>13</v>
@@ -2954,7 +2954,7 @@
         <v>90</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>13</v>
@@ -2983,7 +2983,7 @@
         <v>91</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>13</v>
@@ -3012,7 +3012,7 @@
         <v>92</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>13</v>
@@ -3041,7 +3041,7 @@
         <v>93</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>13</v>
@@ -3070,7 +3070,7 @@
         <v>94</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>13</v>
@@ -3099,7 +3099,7 @@
         <v>95</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>13</v>
@@ -3128,7 +3128,7 @@
         <v>96</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>13</v>
@@ -3157,7 +3157,7 @@
         <v>97</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>13</v>
@@ -3186,7 +3186,7 @@
         <v>98</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>13</v>
@@ -3215,7 +3215,7 @@
         <v>99</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -3244,7 +3244,7 @@
         <v>100</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -3273,7 +3273,7 @@
         <v>101</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>13</v>
@@ -3302,7 +3302,7 @@
         <v>102</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>10</v>
@@ -3331,7 +3331,7 @@
         <v>103</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>14</v>
@@ -3355,7 +3355,7 @@
       <c r="J93" s="2"/>
       <c r="K93" s="1"/>
       <c r="M93" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
@@ -3369,7 +3369,7 @@
         <v>104</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>13</v>
@@ -3398,7 +3398,7 @@
         <v>105</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>10</v>
@@ -3427,7 +3427,7 @@
         <v>106</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>14</v>
@@ -3451,7 +3451,7 @@
       <c r="J97" s="2"/>
       <c r="K97" s="1"/>
       <c r="M97" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
@@ -3465,7 +3465,7 @@
         <v>107</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>13</v>
@@ -3494,7 +3494,7 @@
         <v>108</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>13</v>
@@ -3523,7 +3523,7 @@
         <v>109</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>13</v>
@@ -3552,7 +3552,7 @@
         <v>110</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>13</v>
@@ -3581,7 +3581,7 @@
         <v>111</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>13</v>
@@ -3610,7 +3610,7 @@
         <v>112</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>13</v>
@@ -3639,7 +3639,7 @@
         <v>113</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>13</v>
@@ -3668,7 +3668,7 @@
         <v>114</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>13</v>
@@ -3697,7 +3697,7 @@
         <v>115</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>10</v>
@@ -3726,7 +3726,7 @@
         <v>116</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>13</v>
@@ -3755,7 +3755,7 @@
         <v>117</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>13</v>
@@ -3784,7 +3784,7 @@
         <v>118</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>13</v>
@@ -3813,7 +3813,7 @@
         <v>119</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>10</v>
@@ -3842,7 +3842,7 @@
         <v>120</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>10</v>
@@ -3871,7 +3871,7 @@
         <v>121</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>12</v>
@@ -3895,7 +3895,7 @@
       <c r="J113" s="2"/>
       <c r="K113" s="1"/>
       <c r="M113" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
@@ -3909,7 +3909,7 @@
         <v>122</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>13</v>
@@ -3938,7 +3938,7 @@
         <v>123</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>10</v>
@@ -3967,7 +3967,7 @@
         <v>124</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>14</v>
@@ -3991,7 +3991,7 @@
       <c r="J117" s="2"/>
       <c r="K117" s="1"/>
       <c r="M117" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118" spans="4:13" x14ac:dyDescent="0.3">
@@ -4005,7 +4005,7 @@
         <v>125</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>12</v>
@@ -4029,7 +4029,7 @@
       <c r="J119" s="2"/>
       <c r="K119" s="1"/>
       <c r="M119" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120" spans="4:13" x14ac:dyDescent="0.3">
@@ -4043,7 +4043,7 @@
         <v>126</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>14</v>
@@ -4067,7 +4067,7 @@
       <c r="J121" s="2"/>
       <c r="K121" s="1"/>
       <c r="M121" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="122" spans="4:13" x14ac:dyDescent="0.3">
@@ -4081,7 +4081,7 @@
         <v>127</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>13</v>
@@ -4110,7 +4110,7 @@
         <v>128</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>13</v>
@@ -4139,7 +4139,7 @@
         <v>21</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>13</v>
@@ -4168,7 +4168,7 @@
         <v>22</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>13</v>
@@ -4197,7 +4197,7 @@
         <v>129</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>13</v>
@@ -4226,7 +4226,7 @@
         <v>23</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>13</v>
@@ -4255,7 +4255,7 @@
         <v>24</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>13</v>
@@ -4284,7 +4284,7 @@
         <v>25</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>13</v>
@@ -4313,7 +4313,7 @@
         <v>26</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>14</v>
@@ -4337,7 +4337,7 @@
       <c r="J131" s="2"/>
       <c r="K131" s="1"/>
       <c r="M131" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132" spans="4:13" x14ac:dyDescent="0.3">
@@ -4351,7 +4351,7 @@
         <v>130</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>10</v>
@@ -4380,7 +4380,7 @@
         <v>27</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>13</v>
@@ -4409,7 +4409,7 @@
         <v>28</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>13</v>
@@ -4438,7 +4438,7 @@
         <v>29</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>13</v>
@@ -4467,7 +4467,7 @@
         <v>30</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>13</v>
@@ -4496,7 +4496,7 @@
         <v>32</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>13</v>
@@ -4525,7 +4525,7 @@
         <v>33</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>13</v>
@@ -4554,7 +4554,7 @@
         <v>34</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>10</v>
@@ -4583,7 +4583,7 @@
         <v>35</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>13</v>
@@ -4612,7 +4612,7 @@
         <v>36</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>13</v>
@@ -4641,7 +4641,7 @@
         <v>37</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>13</v>
@@ -4670,7 +4670,7 @@
         <v>39</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>13</v>
@@ -4699,7 +4699,7 @@
         <v>40</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>13</v>
@@ -4728,7 +4728,7 @@
         <v>41</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>12</v>
@@ -4752,7 +4752,7 @@
       <c r="J146" s="2"/>
       <c r="K146" s="1"/>
       <c r="M146" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="147" spans="4:13" x14ac:dyDescent="0.3">
@@ -4766,7 +4766,7 @@
         <v>42</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>13</v>
@@ -4795,7 +4795,7 @@
         <v>43</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>12</v>
@@ -4819,7 +4819,7 @@
       <c r="J149" s="2"/>
       <c r="K149" s="1"/>
       <c r="M149" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150" spans="4:13" x14ac:dyDescent="0.3">
@@ -4833,7 +4833,7 @@
         <v>131</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>13</v>
@@ -4862,7 +4862,7 @@
         <v>44</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>13</v>
@@ -4891,7 +4891,7 @@
         <v>45</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>13</v>
@@ -4920,7 +4920,7 @@
         <v>46</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>13</v>
@@ -4949,7 +4949,7 @@
         <v>47</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>13</v>
@@ -4978,7 +4978,7 @@
         <v>48</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>14</v>
@@ -5002,7 +5002,7 @@
       <c r="J156" s="2"/>
       <c r="K156" s="1"/>
       <c r="M156" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
@@ -5016,7 +5016,7 @@
         <v>49</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>13</v>
@@ -5045,7 +5045,7 @@
         <v>50</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>10</v>
@@ -5074,7 +5074,7 @@
         <v>51</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>13</v>
@@ -5103,7 +5103,7 @@
         <v>52</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>12</v>
@@ -5127,7 +5127,7 @@
       <c r="J161" s="2"/>
       <c r="K161" s="1"/>
       <c r="M161" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="162" spans="4:13" x14ac:dyDescent="0.3">
@@ -5141,7 +5141,7 @@
         <v>53</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>13</v>
@@ -5170,7 +5170,7 @@
         <v>54</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>10</v>
@@ -5199,7 +5199,7 @@
         <v>55</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>13</v>
@@ -5228,7 +5228,7 @@
         <v>56</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>13</v>
@@ -5257,7 +5257,7 @@
         <v>132</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>10</v>
@@ -5286,7 +5286,7 @@
         <v>57</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>13</v>
@@ -5315,7 +5315,7 @@
         <v>58</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>13</v>
@@ -5344,7 +5344,7 @@
         <v>59</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>13</v>
@@ -5373,7 +5373,7 @@
         <v>60</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>13</v>
@@ -5402,7 +5402,7 @@
         <v>61</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>14</v>
@@ -5426,7 +5426,7 @@
       <c r="J172" s="2"/>
       <c r="K172" s="1"/>
       <c r="M172" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="173" spans="4:13" x14ac:dyDescent="0.3">
@@ -5440,7 +5440,7 @@
         <v>62</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>10</v>
@@ -5469,7 +5469,7 @@
         <v>63</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>13</v>
@@ -5498,7 +5498,7 @@
         <v>64</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>13</v>
@@ -5527,7 +5527,7 @@
         <v>65</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>13</v>
@@ -5556,7 +5556,7 @@
         <v>66</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>13</v>
@@ -5585,7 +5585,7 @@
         <v>67</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>13</v>
@@ -5614,7 +5614,7 @@
         <v>68</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>10</v>
@@ -5643,7 +5643,7 @@
         <v>69</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>13</v>
@@ -5672,7 +5672,7 @@
         <v>70</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>13</v>
@@ -5701,7 +5701,7 @@
         <v>71</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>13</v>
@@ -5730,7 +5730,7 @@
         <v>72</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>13</v>
@@ -5759,7 +5759,7 @@
         <v>73</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>13</v>
@@ -5788,7 +5788,7 @@
         <v>133</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>10</v>
@@ -5817,7 +5817,7 @@
         <v>74</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>13</v>
@@ -5846,7 +5846,7 @@
         <v>75</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>14</v>
@@ -5870,7 +5870,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
       <c r="M188" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="189" spans="4:13" x14ac:dyDescent="0.3">
@@ -5884,7 +5884,7 @@
         <v>76</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>13</v>
@@ -5913,7 +5913,7 @@
         <v>77</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>10</v>
@@ -5942,7 +5942,7 @@
         <v>78</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>13</v>
@@ -5971,7 +5971,7 @@
         <v>79</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>13</v>
@@ -6000,7 +6000,7 @@
         <v>80</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>13</v>
@@ -6029,7 +6029,7 @@
         <v>134</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>13</v>
@@ -6058,7 +6058,7 @@
         <v>81</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>13</v>
@@ -6087,7 +6087,7 @@
         <v>82</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>14</v>
@@ -6111,7 +6111,7 @@
       <c r="J197" s="2"/>
       <c r="K197" s="1"/>
       <c r="M197" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="198" spans="4:13" x14ac:dyDescent="0.3">
@@ -6125,7 +6125,7 @@
         <v>83</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>13</v>
@@ -6154,7 +6154,7 @@
         <v>84</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>13</v>
@@ -6183,7 +6183,7 @@
         <v>85</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>13</v>
@@ -6212,7 +6212,7 @@
         <v>86</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>13</v>
@@ -6241,7 +6241,7 @@
         <v>87</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>12</v>
@@ -6265,7 +6265,7 @@
       <c r="J203" s="2"/>
       <c r="K203" s="1"/>
       <c r="M203" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="204" spans="4:13" x14ac:dyDescent="0.3">
@@ -6279,7 +6279,7 @@
         <v>88</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>13</v>
@@ -6308,7 +6308,7 @@
         <v>89</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>13</v>
@@ -6337,7 +6337,7 @@
         <v>90</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>13</v>
@@ -6366,7 +6366,7 @@
         <v>91</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>12</v>
@@ -6390,7 +6390,7 @@
       <c r="J208" s="2"/>
       <c r="K208" s="1"/>
       <c r="M208" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="209" spans="4:13" x14ac:dyDescent="0.3">
@@ -6404,7 +6404,7 @@
         <v>92</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>13</v>
@@ -6433,7 +6433,7 @@
         <v>93</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>13</v>
@@ -6462,7 +6462,7 @@
         <v>94</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>10</v>
@@ -6491,7 +6491,7 @@
         <v>95</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>12</v>
@@ -6515,7 +6515,7 @@
       <c r="J213" s="2"/>
       <c r="K213" s="1"/>
       <c r="M213" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="214" spans="4:13" x14ac:dyDescent="0.3">
@@ -6529,7 +6529,7 @@
         <v>96</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>13</v>
@@ -6558,7 +6558,7 @@
         <v>97</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>13</v>
@@ -6587,7 +6587,7 @@
         <v>98</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>12</v>
@@ -6611,7 +6611,7 @@
       <c r="J217" s="2"/>
       <c r="K217" s="1"/>
       <c r="M217" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="218" spans="4:13" x14ac:dyDescent="0.3">
@@ -6625,7 +6625,7 @@
         <v>99</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>13</v>
@@ -6654,7 +6654,7 @@
         <v>101</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>13</v>
@@ -6683,7 +6683,7 @@
         <v>102</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>13</v>
@@ -6712,7 +6712,7 @@
         <v>103</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>13</v>
@@ -6741,7 +6741,7 @@
         <v>104</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>12</v>
@@ -6765,7 +6765,7 @@
       <c r="J223" s="2"/>
       <c r="K223" s="1"/>
       <c r="M223" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="224" spans="4:13" x14ac:dyDescent="0.3">
@@ -6779,7 +6779,7 @@
         <v>105</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>13</v>
@@ -6808,7 +6808,7 @@
         <v>106</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>13</v>
@@ -6837,7 +6837,7 @@
         <v>107</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>13</v>
@@ -6866,7 +6866,7 @@
         <v>108</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>13</v>
@@ -6895,7 +6895,7 @@
         <v>109</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>13</v>
@@ -6924,7 +6924,7 @@
         <v>110</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>13</v>
@@ -6953,7 +6953,7 @@
         <v>111</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>13</v>
@@ -6982,7 +6982,7 @@
         <v>112</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>13</v>
@@ -7011,7 +7011,7 @@
         <v>113</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>13</v>
@@ -7040,7 +7040,7 @@
         <v>114</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>13</v>
@@ -7069,7 +7069,7 @@
         <v>115</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>13</v>
@@ -7098,7 +7098,7 @@
         <v>116</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>13</v>
@@ -7127,7 +7127,7 @@
         <v>117</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>13</v>
@@ -7156,7 +7156,7 @@
         <v>118</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>13</v>
@@ -7185,7 +7185,7 @@
         <v>119</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>13</v>
@@ -7214,7 +7214,7 @@
         <v>120</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>13</v>
@@ -7243,7 +7243,7 @@
         <v>121</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>13</v>
@@ -7272,7 +7272,7 @@
         <v>122</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>13</v>
@@ -7301,7 +7301,7 @@
         <v>123</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>13</v>
@@ -7330,7 +7330,7 @@
         <v>124</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>13</v>
@@ -7359,7 +7359,7 @@
         <v>125</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>12</v>
@@ -7383,7 +7383,7 @@
       <c r="J245" s="2"/>
       <c r="K245" s="1"/>
       <c r="M245" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="246" spans="4:13" x14ac:dyDescent="0.3">
@@ -7397,7 +7397,7 @@
         <v>126</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>13</v>
@@ -7426,7 +7426,7 @@
         <v>127</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>13</v>
@@ -7455,7 +7455,7 @@
         <v>128</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>13</v>
@@ -7484,7 +7484,7 @@
         <v>21</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>13</v>
@@ -7513,7 +7513,7 @@
         <v>22</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>13</v>
@@ -7542,7 +7542,7 @@
         <v>129</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>13</v>
@@ -7571,7 +7571,7 @@
         <v>23</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7600,7 +7600,7 @@
         <v>24</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>13</v>
@@ -7629,7 +7629,7 @@
         <v>25</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>13</v>
@@ -7658,7 +7658,7 @@
         <v>26</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>14</v>
@@ -7682,7 +7682,7 @@
       <c r="J256" s="2"/>
       <c r="K256" s="1"/>
       <c r="M256" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="257" spans="4:13" x14ac:dyDescent="0.3">
@@ -7696,7 +7696,7 @@
         <v>130</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>13</v>
@@ -7725,7 +7725,7 @@
         <v>27</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>13</v>
@@ -7754,7 +7754,7 @@
         <v>28</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>10</v>
@@ -7783,7 +7783,7 @@
         <v>29</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>13</v>
@@ -7812,7 +7812,7 @@
         <v>30</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>10</v>
@@ -7841,7 +7841,7 @@
         <v>32</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>13</v>
@@ -7870,7 +7870,7 @@
         <v>33</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>13</v>
@@ -7899,7 +7899,7 @@
         <v>34</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>10</v>
@@ -7928,7 +7928,7 @@
         <v>35</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>13</v>
@@ -7957,7 +7957,7 @@
         <v>36</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>13</v>
@@ -7986,7 +7986,7 @@
         <v>37</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>13</v>
@@ -8015,7 +8015,7 @@
         <v>39</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>13</v>
@@ -8044,7 +8044,7 @@
         <v>40</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>10</v>
@@ -8073,7 +8073,7 @@
         <v>41</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>13</v>
@@ -8102,7 +8102,7 @@
         <v>42</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>13</v>
@@ -8131,7 +8131,7 @@
         <v>135</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>13</v>
@@ -8160,7 +8160,7 @@
         <v>43</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>14</v>
@@ -8184,7 +8184,7 @@
       <c r="J274" s="2"/>
       <c r="K274" s="1"/>
       <c r="M274" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="275" spans="4:13" x14ac:dyDescent="0.3">
@@ -8198,7 +8198,7 @@
         <v>131</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>12</v>
@@ -8222,7 +8222,7 @@
       <c r="J276" s="2"/>
       <c r="K276" s="1"/>
       <c r="M276" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="277" spans="4:13" x14ac:dyDescent="0.3">
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>13</v>
@@ -8265,7 +8265,7 @@
         <v>45</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>10</v>
@@ -8294,7 +8294,7 @@
         <v>46</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>13</v>
@@ -8323,7 +8323,7 @@
         <v>47</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>13</v>
@@ -8352,7 +8352,7 @@
         <v>48</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>13</v>
@@ -8381,7 +8381,7 @@
         <v>49</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>10</v>
@@ -8410,7 +8410,7 @@
         <v>50</v>
       </c>
       <c r="H283" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>13</v>
@@ -8439,7 +8439,7 @@
         <v>51</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>13</v>
@@ -8468,7 +8468,7 @@
         <v>52</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>14</v>
@@ -8492,7 +8492,7 @@
       <c r="J286" s="2"/>
       <c r="K286" s="1"/>
       <c r="M286" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="287" spans="4:13" x14ac:dyDescent="0.3">
@@ -8506,7 +8506,7 @@
         <v>53</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>12</v>
@@ -8530,7 +8530,7 @@
       <c r="J288" s="2"/>
       <c r="K288" s="1"/>
       <c r="M288" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="289" spans="4:13" x14ac:dyDescent="0.3">
@@ -8544,7 +8544,7 @@
         <v>54</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>10</v>
@@ -8573,7 +8573,7 @@
         <v>55</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>13</v>
@@ -8602,7 +8602,7 @@
         <v>56</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>13</v>
@@ -8631,7 +8631,7 @@
         <v>132</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>10</v>
@@ -8660,7 +8660,7 @@
         <v>57</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>13</v>
@@ -8689,7 +8689,7 @@
         <v>58</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>13</v>
@@ -8718,7 +8718,7 @@
         <v>59</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>13</v>
@@ -8747,7 +8747,7 @@
         <v>60</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>13</v>
@@ -8776,7 +8776,7 @@
         <v>61</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>10</v>
@@ -8805,7 +8805,7 @@
         <v>62</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>10</v>
@@ -8834,7 +8834,7 @@
         <v>63</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>13</v>
@@ -8863,7 +8863,7 @@
         <v>64</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>13</v>
@@ -8892,7 +8892,7 @@
         <v>65</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>10</v>
@@ -8921,7 +8921,7 @@
         <v>66</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>13</v>
@@ -8950,7 +8950,7 @@
         <v>67</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>13</v>
@@ -8979,7 +8979,7 @@
         <v>68</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>10</v>
@@ -9008,7 +9008,7 @@
         <v>69</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>13</v>
@@ -9037,7 +9037,7 @@
         <v>70</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>13</v>
@@ -9066,7 +9066,7 @@
         <v>71</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>13</v>
@@ -9095,7 +9095,7 @@
         <v>72</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>13</v>
@@ -9124,7 +9124,7 @@
         <v>73</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>13</v>
@@ -9153,7 +9153,7 @@
         <v>133</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>13</v>
@@ -9182,7 +9182,7 @@
         <v>74</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>13</v>
@@ -9211,7 +9211,7 @@
         <v>75</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>13</v>
@@ -9240,7 +9240,7 @@
         <v>76</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>13</v>
@@ -9269,7 +9269,7 @@
         <v>77</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>13</v>
@@ -9298,7 +9298,7 @@
         <v>78</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I315" s="1" t="s">
         <v>13</v>
@@ -9327,7 +9327,7 @@
         <v>79</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>13</v>
@@ -9356,7 +9356,7 @@
         <v>80</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>13</v>
@@ -9385,7 +9385,7 @@
         <v>134</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>13</v>
@@ -9414,7 +9414,7 @@
         <v>81</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>13</v>
@@ -9443,7 +9443,7 @@
         <v>82</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>10</v>
@@ -9472,7 +9472,7 @@
         <v>83</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>13</v>
@@ -9501,7 +9501,7 @@
         <v>84</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>13</v>
@@ -9530,7 +9530,7 @@
         <v>85</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I323" s="1" t="s">
         <v>13</v>
@@ -9559,7 +9559,7 @@
         <v>86</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>13</v>
@@ -9588,7 +9588,7 @@
         <v>87</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I325" s="1" t="s">
         <v>13</v>
@@ -9617,7 +9617,7 @@
         <v>88</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>13</v>
@@ -9646,7 +9646,7 @@
         <v>89</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I327" s="1" t="s">
         <v>12</v>
@@ -9670,7 +9670,7 @@
       <c r="J328" s="2"/>
       <c r="K328" s="1"/>
       <c r="M328" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="329" spans="4:13" x14ac:dyDescent="0.3">
@@ -9684,7 +9684,7 @@
         <v>90</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>10</v>
@@ -9713,7 +9713,7 @@
         <v>91</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>12</v>
@@ -9737,7 +9737,7 @@
       <c r="J331" s="2"/>
       <c r="K331" s="1"/>
       <c r="M331" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="332" spans="4:13" x14ac:dyDescent="0.3">
@@ -9751,7 +9751,7 @@
         <v>92</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>13</v>
@@ -9780,7 +9780,7 @@
         <v>93</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>13</v>
@@ -9809,7 +9809,7 @@
         <v>94</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>13</v>
@@ -9838,7 +9838,7 @@
         <v>95</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I335" s="1" t="s">
         <v>13</v>
@@ -9867,7 +9867,7 @@
         <v>96</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>13</v>
@@ -9896,7 +9896,7 @@
         <v>97</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>13</v>
@@ -9925,7 +9925,7 @@
         <v>98</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>13</v>
@@ -9954,7 +9954,7 @@
         <v>99</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>13</v>
@@ -9983,7 +9983,7 @@
         <v>101</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>13</v>
@@ -10012,7 +10012,7 @@
         <v>102</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>13</v>
@@ -10041,7 +10041,7 @@
         <v>103</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>10</v>
@@ -10070,7 +10070,7 @@
         <v>104</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>13</v>
@@ -10099,7 +10099,7 @@
         <v>105</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>13</v>
@@ -10128,7 +10128,7 @@
         <v>106</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>13</v>
@@ -10157,7 +10157,7 @@
         <v>107</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I346" s="1" t="s">
         <v>13</v>
@@ -10186,7 +10186,7 @@
         <v>108</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I347" s="1" t="s">
         <v>13</v>
@@ -10215,7 +10215,7 @@
         <v>109</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>13</v>
@@ -10244,7 +10244,7 @@
         <v>110</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>10</v>
@@ -10273,7 +10273,7 @@
         <v>111</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>13</v>
@@ -10302,7 +10302,7 @@
         <v>112</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>13</v>
@@ -10331,7 +10331,7 @@
         <v>113</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>13</v>
@@ -10360,7 +10360,7 @@
         <v>114</v>
       </c>
       <c r="H353" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>13</v>
@@ -10389,7 +10389,7 @@
         <v>115</v>
       </c>
       <c r="H354" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I354" s="1" t="s">
         <v>13</v>
@@ -10418,7 +10418,7 @@
         <v>116</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I355" s="1" t="s">
         <v>13</v>
@@ -10447,7 +10447,7 @@
         <v>117</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I356" s="1" t="s">
         <v>13</v>
@@ -10476,7 +10476,7 @@
         <v>118</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I357" s="1" t="s">
         <v>13</v>
@@ -10505,7 +10505,7 @@
         <v>119</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I358" s="1" t="s">
         <v>13</v>
@@ -10534,7 +10534,7 @@
         <v>120</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I359" s="1" t="s">
         <v>10</v>
@@ -10563,7 +10563,7 @@
         <v>121</v>
       </c>
       <c r="H360" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I360" s="1" t="s">
         <v>12</v>
@@ -10587,7 +10587,7 @@
       <c r="J361" s="2"/>
       <c r="K361" s="1"/>
       <c r="M361" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="362" spans="4:13" x14ac:dyDescent="0.3">
@@ -10601,7 +10601,7 @@
         <v>122</v>
       </c>
       <c r="H362" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I362" s="1" t="s">
         <v>13</v>
@@ -10630,7 +10630,7 @@
         <v>123</v>
       </c>
       <c r="H363" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I363" s="1" t="s">
         <v>13</v>
@@ -10659,7 +10659,7 @@
         <v>124</v>
       </c>
       <c r="H364" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I364" s="1" t="s">
         <v>13</v>
@@ -10688,7 +10688,7 @@
         <v>125</v>
       </c>
       <c r="H365" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I365" s="1" t="s">
         <v>10</v>
@@ -10717,7 +10717,7 @@
         <v>126</v>
       </c>
       <c r="H366" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I366" s="1" t="s">
         <v>13</v>
@@ -10746,7 +10746,7 @@
         <v>127</v>
       </c>
       <c r="H367" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>13</v>
@@ -10775,7 +10775,7 @@
         <v>128</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>13</v>
@@ -10804,7 +10804,7 @@
         <v>21</v>
       </c>
       <c r="H369" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I369" s="1" t="s">
         <v>13</v>
@@ -10833,7 +10833,7 @@
         <v>136</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>12</v>
@@ -10857,7 +10857,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
       <c r="M371" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="372" spans="4:13" x14ac:dyDescent="0.3">
@@ -10871,7 +10871,7 @@
         <v>22</v>
       </c>
       <c r="H372" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I372" s="1" t="s">
         <v>13</v>
@@ -10900,7 +10900,7 @@
         <v>129</v>
       </c>
       <c r="H373" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I373" s="1" t="s">
         <v>14</v>
@@ -10924,7 +10924,7 @@
       <c r="J374" s="2"/>
       <c r="K374" s="1"/>
       <c r="M374" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="375" spans="4:13" x14ac:dyDescent="0.3">
@@ -10938,7 +10938,7 @@
         <v>23</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>13</v>
@@ -10967,7 +10967,7 @@
         <v>24</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>13</v>
@@ -10996,7 +10996,7 @@
         <v>25</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I377" s="1" t="s">
         <v>13</v>
@@ -11025,7 +11025,7 @@
         <v>26</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I378" s="1" t="s">
         <v>13</v>
@@ -11054,7 +11054,7 @@
         <v>130</v>
       </c>
       <c r="H379" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I379" s="1" t="s">
         <v>13</v>
@@ -11083,7 +11083,7 @@
         <v>27</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I380" s="1" t="s">
         <v>13</v>
@@ -11112,7 +11112,7 @@
         <v>28</v>
       </c>
       <c r="H381" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I381" s="1" t="s">
         <v>12</v>
@@ -11136,7 +11136,7 @@
       <c r="J382" s="2"/>
       <c r="K382" s="1"/>
       <c r="M382" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="383" spans="4:13" x14ac:dyDescent="0.3">
@@ -11150,7 +11150,7 @@
         <v>30</v>
       </c>
       <c r="H383" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I383" s="1" t="s">
         <v>13</v>
@@ -11179,7 +11179,7 @@
         <v>32</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>13</v>
@@ -11208,7 +11208,7 @@
         <v>33</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I385" s="1" t="s">
         <v>13</v>
@@ -11237,7 +11237,7 @@
         <v>34</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I386" s="1" t="s">
         <v>10</v>
@@ -11266,7 +11266,7 @@
         <v>35</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I387" s="1" t="s">
         <v>13</v>
@@ -11295,7 +11295,7 @@
         <v>36</v>
       </c>
       <c r="H388" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I388" s="1" t="s">
         <v>13</v>
@@ -11324,7 +11324,7 @@
         <v>37</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I389" s="1" t="s">
         <v>13</v>
@@ -11353,7 +11353,7 @@
         <v>39</v>
       </c>
       <c r="H390" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I390" s="1" t="s">
         <v>13</v>
@@ -11382,7 +11382,7 @@
         <v>40</v>
       </c>
       <c r="H391" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I391" s="1" t="s">
         <v>13</v>
@@ -11411,7 +11411,7 @@
         <v>41</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I392" s="1" t="s">
         <v>13</v>
@@ -11440,7 +11440,7 @@
         <v>135</v>
       </c>
       <c r="H393" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I393" s="1" t="s">
         <v>13</v>
@@ -11469,7 +11469,7 @@
         <v>43</v>
       </c>
       <c r="H394" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I394" s="1" t="s">
         <v>13</v>
@@ -11498,7 +11498,7 @@
         <v>131</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I395" s="1" t="s">
         <v>13</v>
@@ -11527,7 +11527,7 @@
         <v>44</v>
       </c>
       <c r="H396" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I396" s="1" t="s">
         <v>13</v>
@@ -11556,7 +11556,7 @@
         <v>45</v>
       </c>
       <c r="H397" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I397" s="1" t="s">
         <v>12</v>
@@ -11580,7 +11580,7 @@
       <c r="J398" s="2"/>
       <c r="K398" s="1"/>
       <c r="M398" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="399" spans="4:13" x14ac:dyDescent="0.3">
@@ -11594,7 +11594,7 @@
         <v>46</v>
       </c>
       <c r="H399" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I399" s="1" t="s">
         <v>13</v>
@@ -11623,7 +11623,7 @@
         <v>49</v>
       </c>
       <c r="H400" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I400" s="1" t="s">
         <v>10</v>
@@ -11652,7 +11652,7 @@
         <v>50</v>
       </c>
       <c r="H401" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I401" s="1" t="s">
         <v>13</v>
@@ -11681,7 +11681,7 @@
         <v>51</v>
       </c>
       <c r="H402" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I402" s="1" t="s">
         <v>13</v>
@@ -11710,7 +11710,7 @@
         <v>52</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I403" s="1" t="s">
         <v>13</v>
@@ -11739,7 +11739,7 @@
         <v>53</v>
       </c>
       <c r="H404" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I404" s="1" t="s">
         <v>13</v>
@@ -11768,7 +11768,7 @@
         <v>54</v>
       </c>
       <c r="H405" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I405" s="1" t="s">
         <v>10</v>
@@ -11797,7 +11797,7 @@
         <v>55</v>
       </c>
       <c r="H406" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I406" s="1" t="s">
         <v>13</v>
@@ -11826,7 +11826,7 @@
         <v>56</v>
       </c>
       <c r="H407" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I407" s="1" t="s">
         <v>13</v>
@@ -11855,7 +11855,7 @@
         <v>132</v>
       </c>
       <c r="H408" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I408" s="1" t="s">
         <v>10</v>
@@ -11884,7 +11884,7 @@
         <v>57</v>
       </c>
       <c r="H409" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I409" s="1" t="s">
         <v>13</v>
@@ -11913,7 +11913,7 @@
         <v>58</v>
       </c>
       <c r="H410" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I410" s="1" t="s">
         <v>13</v>
@@ -11942,7 +11942,7 @@
         <v>59</v>
       </c>
       <c r="H411" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I411" s="1" t="s">
         <v>13</v>
@@ -11971,7 +11971,7 @@
         <v>60</v>
       </c>
       <c r="H412" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I412" s="1" t="s">
         <v>13</v>
@@ -12000,7 +12000,7 @@
         <v>61</v>
       </c>
       <c r="H413" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I413" s="1" t="s">
         <v>10</v>
@@ -12029,7 +12029,7 @@
         <v>62</v>
       </c>
       <c r="H414" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I414" s="1" t="s">
         <v>13</v>
@@ -12058,7 +12058,7 @@
         <v>63</v>
       </c>
       <c r="H415" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I415" s="1" t="s">
         <v>13</v>
@@ -12087,7 +12087,7 @@
         <v>64</v>
       </c>
       <c r="H416" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I416" s="1" t="s">
         <v>13</v>
@@ -12116,7 +12116,7 @@
         <v>65</v>
       </c>
       <c r="H417" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I417" s="1" t="s">
         <v>12</v>
@@ -12140,7 +12140,7 @@
       <c r="J418" s="2"/>
       <c r="K418" s="1"/>
       <c r="M418" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="419" spans="4:13" x14ac:dyDescent="0.3">
@@ -12154,7 +12154,7 @@
         <v>66</v>
       </c>
       <c r="H419" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I419" s="1" t="s">
         <v>10</v>
@@ -12183,7 +12183,7 @@
         <v>67</v>
       </c>
       <c r="H420" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I420" s="1" t="s">
         <v>14</v>
@@ -12207,7 +12207,7 @@
       <c r="J421" s="2"/>
       <c r="K421" s="1"/>
       <c r="M421" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="422" spans="4:13" x14ac:dyDescent="0.3">
@@ -12221,7 +12221,7 @@
         <v>68</v>
       </c>
       <c r="H422" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I422" s="1" t="s">
         <v>10</v>
@@ -12250,7 +12250,7 @@
         <v>69</v>
       </c>
       <c r="H423" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I423" s="1" t="s">
         <v>13</v>
@@ -12279,7 +12279,7 @@
         <v>70</v>
       </c>
       <c r="H424" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I424" s="1" t="s">
         <v>13</v>
@@ -12308,7 +12308,7 @@
         <v>71</v>
       </c>
       <c r="H425" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I425" s="1" t="s">
         <v>13</v>
@@ -12337,7 +12337,7 @@
         <v>72</v>
       </c>
       <c r="H426" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I426" s="1" t="s">
         <v>13</v>
@@ -12366,7 +12366,7 @@
         <v>74</v>
       </c>
       <c r="H427" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I427" s="1" t="s">
         <v>13</v>
@@ -12395,7 +12395,7 @@
         <v>75</v>
       </c>
       <c r="H428" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I428" s="1" t="s">
         <v>13</v>
@@ -12424,7 +12424,7 @@
         <v>76</v>
       </c>
       <c r="H429" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I429" s="1" t="s">
         <v>13</v>
@@ -12453,7 +12453,7 @@
         <v>77</v>
       </c>
       <c r="H430" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I430" s="1" t="s">
         <v>13</v>
@@ -12482,7 +12482,7 @@
         <v>80</v>
       </c>
       <c r="H431" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I431" s="1" t="s">
         <v>13</v>
@@ -12511,7 +12511,7 @@
         <v>134</v>
       </c>
       <c r="H432" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I432" s="1" t="s">
         <v>13</v>
@@ -12540,7 +12540,7 @@
         <v>81</v>
       </c>
       <c r="H433" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I433" s="1" t="s">
         <v>13</v>
@@ -12569,7 +12569,7 @@
         <v>82</v>
       </c>
       <c r="H434" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I434" s="1" t="s">
         <v>13</v>
@@ -12598,7 +12598,7 @@
         <v>83</v>
       </c>
       <c r="H435" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I435" s="1" t="s">
         <v>13</v>
@@ -12627,7 +12627,7 @@
         <v>84</v>
       </c>
       <c r="H436" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I436" s="1" t="s">
         <v>13</v>
@@ -12656,7 +12656,7 @@
         <v>85</v>
       </c>
       <c r="H437" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I437" s="1" t="s">
         <v>13</v>
@@ -12685,7 +12685,7 @@
         <v>87</v>
       </c>
       <c r="H438" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I438" s="1" t="s">
         <v>13</v>
@@ -12714,7 +12714,7 @@
         <v>89</v>
       </c>
       <c r="H439" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I439" s="1" t="s">
         <v>12</v>
@@ -12738,7 +12738,7 @@
       <c r="J440" s="2"/>
       <c r="K440" s="1"/>
       <c r="M440" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="441" spans="4:13" x14ac:dyDescent="0.3">
@@ -12752,7 +12752,7 @@
         <v>90</v>
       </c>
       <c r="H441" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I441" s="1" t="s">
         <v>13</v>
@@ -12781,7 +12781,7 @@
         <v>91</v>
       </c>
       <c r="H442" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I442" s="1" t="s">
         <v>12</v>
@@ -12805,7 +12805,7 @@
       <c r="J443" s="2"/>
       <c r="K443" s="1"/>
       <c r="M443" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="444" spans="4:13" x14ac:dyDescent="0.3">
@@ -12819,7 +12819,7 @@
         <v>92</v>
       </c>
       <c r="H444" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I444" s="1" t="s">
         <v>13</v>
@@ -12848,7 +12848,7 @@
         <v>93</v>
       </c>
       <c r="H445" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I445" s="1" t="s">
         <v>13</v>
@@ -12877,7 +12877,7 @@
         <v>94</v>
       </c>
       <c r="H446" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I446" s="1" t="s">
         <v>13</v>
@@ -12906,7 +12906,7 @@
         <v>95</v>
       </c>
       <c r="H447" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I447" s="1" t="s">
         <v>12</v>
@@ -12930,7 +12930,7 @@
       <c r="J448" s="2"/>
       <c r="K448" s="1"/>
       <c r="M448" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="449" spans="4:13" x14ac:dyDescent="0.3">
@@ -12944,7 +12944,7 @@
         <v>96</v>
       </c>
       <c r="H449" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I449" s="1" t="s">
         <v>13</v>
@@ -12973,7 +12973,7 @@
         <v>97</v>
       </c>
       <c r="H450" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I450" s="1" t="s">
         <v>13</v>
@@ -13002,7 +13002,7 @@
         <v>98</v>
       </c>
       <c r="H451" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I451" s="1" t="s">
         <v>13</v>
@@ -13031,7 +13031,7 @@
         <v>99</v>
       </c>
       <c r="H452" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I452" s="1" t="s">
         <v>13</v>
@@ -13060,7 +13060,7 @@
         <v>101</v>
       </c>
       <c r="H453" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I453" s="1" t="s">
         <v>13</v>
@@ -13089,7 +13089,7 @@
         <v>102</v>
       </c>
       <c r="H454" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I454" s="1" t="s">
         <v>13</v>
@@ -13118,7 +13118,7 @@
         <v>103</v>
       </c>
       <c r="H455" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I455" s="1" t="s">
         <v>13</v>
@@ -13147,7 +13147,7 @@
         <v>104</v>
       </c>
       <c r="H456" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I456" s="1" t="s">
         <v>13</v>
@@ -13176,7 +13176,7 @@
         <v>105</v>
       </c>
       <c r="H457" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I457" s="1" t="s">
         <v>13</v>
@@ -13205,7 +13205,7 @@
         <v>106</v>
       </c>
       <c r="H458" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I458" s="1" t="s">
         <v>13</v>
@@ -13234,7 +13234,7 @@
         <v>107</v>
       </c>
       <c r="H459" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I459" s="1" t="s">
         <v>13</v>
@@ -13263,7 +13263,7 @@
         <v>108</v>
       </c>
       <c r="H460" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I460" s="1" t="s">
         <v>13</v>
@@ -13292,7 +13292,7 @@
         <v>109</v>
       </c>
       <c r="H461" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I461" s="1" t="s">
         <v>13</v>
@@ -13321,7 +13321,7 @@
         <v>110</v>
       </c>
       <c r="H462" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I462" s="1" t="s">
         <v>13</v>
@@ -13350,7 +13350,7 @@
         <v>111</v>
       </c>
       <c r="H463" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I463" s="1" t="s">
         <v>13</v>
@@ -13379,7 +13379,7 @@
         <v>112</v>
       </c>
       <c r="H464" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I464" s="1" t="s">
         <v>13</v>
@@ -13408,7 +13408,7 @@
         <v>113</v>
       </c>
       <c r="H465" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I465" s="1" t="s">
         <v>13</v>
@@ -13437,7 +13437,7 @@
         <v>114</v>
       </c>
       <c r="H466" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I466" s="1" t="s">
         <v>14</v>
@@ -13461,7 +13461,7 @@
       <c r="J467" s="2"/>
       <c r="K467" s="1"/>
       <c r="M467" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="468" spans="4:13" x14ac:dyDescent="0.3">
@@ -13475,7 +13475,7 @@
         <v>116</v>
       </c>
       <c r="H468" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I468" s="1" t="s">
         <v>10</v>
@@ -13504,7 +13504,7 @@
         <v>117</v>
       </c>
       <c r="H469" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I469" s="1" t="s">
         <v>13</v>
@@ -13533,7 +13533,7 @@
         <v>118</v>
       </c>
       <c r="H470" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I470" s="1" t="s">
         <v>13</v>
@@ -13562,7 +13562,7 @@
         <v>119</v>
       </c>
       <c r="H471" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I471" s="1" t="s">
         <v>13</v>
@@ -13591,7 +13591,7 @@
         <v>120</v>
       </c>
       <c r="H472" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I472" s="1" t="s">
         <v>12</v>
@@ -13615,7 +13615,7 @@
       <c r="J473" s="2"/>
       <c r="K473" s="1"/>
       <c r="M473" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="474" spans="4:13" x14ac:dyDescent="0.3">
@@ -13629,7 +13629,7 @@
         <v>121</v>
       </c>
       <c r="H474" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I474" s="1" t="s">
         <v>13</v>
@@ -13658,7 +13658,7 @@
         <v>122</v>
       </c>
       <c r="H475" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I475" s="1" t="s">
         <v>12</v>
@@ -13682,7 +13682,7 @@
       <c r="J476" s="2"/>
       <c r="K476" s="1"/>
       <c r="M476" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="477" spans="4:13" x14ac:dyDescent="0.3">
@@ -13696,7 +13696,7 @@
         <v>124</v>
       </c>
       <c r="H477" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I477" s="1" t="s">
         <v>13</v>
@@ -13725,7 +13725,7 @@
         <v>125</v>
       </c>
       <c r="H478" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I478" s="1" t="s">
         <v>13</v>
@@ -13754,7 +13754,7 @@
         <v>126</v>
       </c>
       <c r="H479" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I479" s="1" t="s">
         <v>13</v>
@@ -13783,7 +13783,7 @@
         <v>127</v>
       </c>
       <c r="H480" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I480" s="1" t="s">
         <v>13</v>
@@ -13812,7 +13812,7 @@
         <v>128</v>
       </c>
       <c r="H481" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I481" s="1" t="s">
         <v>13</v>
@@ -15122,6 +15122,7 @@
     <row r="697" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H697" s="2"/>
       <c r="I697" s="1"/>
+      <c r="J697" s="2"/>
       <c r="K697" s="1"/>
     </row>
     <row r="698" spans="8:11" x14ac:dyDescent="0.3">
@@ -15431,6 +15432,7 @@
     <row r="749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H749" s="2"/>
       <c r="I749" s="1"/>
+      <c r="J749" s="2"/>
       <c r="K749" s="1"/>
     </row>
     <row r="750" spans="8:11" x14ac:dyDescent="0.3">
@@ -15520,6 +15522,7 @@
     <row r="764" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H764" s="2"/>
       <c r="I764" s="1"/>
+      <c r="J764" s="2"/>
       <c r="K764" s="1"/>
     </row>
     <row r="765" spans="8:11" x14ac:dyDescent="0.3">
@@ -15626,6 +15629,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -15643,6 +15647,7 @@
     <row r="785" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H785" s="2"/>
       <c r="I785" s="1"/>
+      <c r="J785" s="2"/>
       <c r="K785" s="1"/>
     </row>
     <row r="786" spans="8:11" x14ac:dyDescent="0.3">
@@ -15654,6 +15659,7 @@
     <row r="787" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H787" s="2"/>
       <c r="I787" s="1"/>
+      <c r="J787" s="2"/>
       <c r="K787" s="1"/>
     </row>
     <row r="788" spans="8:11" x14ac:dyDescent="0.3">
@@ -15695,6 +15701,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -15718,6 +15725,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -15741,6 +15749,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -15758,6 +15767,7 @@
     <row r="805" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H805" s="2"/>
       <c r="I805" s="1"/>
+      <c r="J805" s="2"/>
       <c r="K805" s="1"/>
     </row>
     <row r="806" spans="8:11" x14ac:dyDescent="0.3">
@@ -15769,11 +15779,13 @@
     <row r="807" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H807" s="2"/>
       <c r="I807" s="1"/>
+      <c r="J807" s="2"/>
       <c r="K807" s="1"/>
     </row>
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H808" s="2"/>
       <c r="I808" s="1"/>
+      <c r="J808" s="2"/>
       <c r="K808" s="1"/>
     </row>
     <row r="809" spans="8:11" x14ac:dyDescent="0.3">
@@ -15893,6 +15905,7 @@
     <row r="828" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H828" s="2"/>
       <c r="I828" s="1"/>
+      <c r="J828" s="2"/>
       <c r="K828" s="1"/>
     </row>
     <row r="829" spans="8:11" x14ac:dyDescent="0.3">
@@ -15976,6 +15989,7 @@
     <row r="842" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H842" s="2"/>
       <c r="I842" s="1"/>
+      <c r="J842" s="2"/>
       <c r="K842" s="1"/>
     </row>
     <row r="843" spans="8:11" x14ac:dyDescent="0.3">
@@ -15999,6 +16013,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -16010,6 +16025,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -16021,6 +16037,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -16068,6 +16085,7 @@
     <row r="858" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H858" s="2"/>
       <c r="I858" s="1"/>
+      <c r="J858" s="2"/>
       <c r="K858" s="1"/>
     </row>
     <row r="859" spans="8:11" x14ac:dyDescent="0.3">
@@ -16121,6 +16139,7 @@
     <row r="867" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H867" s="2"/>
       <c r="I867" s="1"/>
+      <c r="J867" s="2"/>
       <c r="K867" s="1"/>
     </row>
     <row r="868" spans="8:11" x14ac:dyDescent="0.3">
@@ -16293,6 +16312,7 @@
     <row r="896" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H896" s="2"/>
       <c r="I896" s="1"/>
+      <c r="J896" s="2"/>
       <c r="K896" s="1"/>
     </row>
     <row r="897" spans="8:11" x14ac:dyDescent="0.3">
@@ -16304,6 +16324,7 @@
     <row r="898" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H898" s="2"/>
       <c r="I898" s="1"/>
+      <c r="J898" s="2"/>
       <c r="K898" s="1"/>
     </row>
     <row r="899" spans="8:11" x14ac:dyDescent="0.3">
@@ -16381,6 +16402,7 @@
     <row r="911" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
+      <c r="J911" s="2"/>
       <c r="K911" s="1"/>
     </row>
     <row r="912" spans="8:11" x14ac:dyDescent="0.3">
@@ -16398,6 +16420,7 @@
     <row r="914" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H914" s="2"/>
       <c r="I914" s="1"/>
+      <c r="J914" s="2"/>
       <c r="K914" s="1"/>
     </row>
     <row r="915" spans="8:11" x14ac:dyDescent="0.3">
@@ -16445,6 +16468,7 @@
     <row r="922" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H922" s="2"/>
       <c r="I922" s="1"/>
+      <c r="J922" s="2"/>
       <c r="K922" s="1"/>
     </row>
     <row r="923" spans="8:11" x14ac:dyDescent="0.3">
@@ -16557,6 +16581,7 @@
     <row r="941" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H941" s="2"/>
       <c r="I941" s="1"/>
+      <c r="J941" s="2"/>
       <c r="K941" s="1"/>
     </row>
     <row r="942" spans="8:11" x14ac:dyDescent="0.3">
@@ -16616,6 +16641,7 @@
     <row r="951" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H951" s="2"/>
       <c r="I951" s="1"/>
+      <c r="J951" s="2"/>
       <c r="K951" s="1"/>
     </row>
     <row r="952" spans="8:11" x14ac:dyDescent="0.3">
@@ -16627,6 +16653,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -16698,6 +16725,7 @@
     <row r="965" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H965" s="2"/>
       <c r="I965" s="1"/>
+      <c r="J965" s="2"/>
       <c r="K965" s="1"/>
     </row>
     <row r="966" spans="8:11" x14ac:dyDescent="0.3">
@@ -16750,6 +16778,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -16826,11 +16855,13 @@
     <row r="987" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H987" s="2"/>
       <c r="I987" s="1"/>
+      <c r="J987" s="2"/>
       <c r="K987" s="1"/>
     </row>
     <row r="988" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H988" s="2"/>
       <c r="I988" s="1"/>
+      <c r="J988" s="2"/>
       <c r="K988" s="1"/>
     </row>
     <row r="989" spans="8:11" x14ac:dyDescent="0.3">
@@ -16890,6 +16921,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -16901,6 +16933,7 @@
     <row r="1000" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1000" s="2"/>
       <c r="I1000" s="1"/>
+      <c r="J1000" s="2"/>
       <c r="K1000" s="1"/>
     </row>
     <row r="1001" spans="8:11" x14ac:dyDescent="0.3">
@@ -16912,11 +16945,13 @@
     <row r="1002" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1002" s="2"/>
       <c r="I1002" s="1"/>
+      <c r="J1002" s="2"/>
       <c r="K1002" s="1"/>
     </row>
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -16970,6 +17005,7 @@
     <row r="1012" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1012" s="2"/>
       <c r="I1012" s="1"/>
+      <c r="J1012" s="2"/>
       <c r="K1012" s="1"/>
     </row>
     <row r="1013" spans="8:11" x14ac:dyDescent="0.3">
@@ -16986,6 +17022,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -17009,6 +17046,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -17026,6 +17064,7 @@
     <row r="1022" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1022" s="2"/>
       <c r="I1022" s="1"/>
+      <c r="J1022" s="2"/>
       <c r="K1022" s="1"/>
     </row>
     <row r="1023" spans="8:11" x14ac:dyDescent="0.3">
@@ -17072,11 +17111,13 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1031" s="2"/>
       <c r="I1031" s="1"/>
+      <c r="J1031" s="2"/>
       <c r="K1031" s="1"/>
     </row>
     <row r="1032" spans="8:11" x14ac:dyDescent="0.3">
@@ -17118,11 +17159,13 @@
     <row r="1038" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1038" s="2"/>
       <c r="I1038" s="1"/>
+      <c r="J1038" s="2"/>
       <c r="K1038" s="1"/>
     </row>
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -17140,6 +17183,7 @@
     <row r="1042" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1042" s="2"/>
       <c r="I1042" s="1"/>
+      <c r="J1042" s="2"/>
       <c r="K1042" s="1"/>
     </row>
     <row r="1043" spans="8:11" x14ac:dyDescent="0.3">
@@ -17151,6 +17195,7 @@
     <row r="1044" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1044" s="2"/>
       <c r="I1044" s="1"/>
+      <c r="J1044" s="2"/>
       <c r="K1044" s="1"/>
     </row>
     <row r="1045" spans="8:11" x14ac:dyDescent="0.3">
@@ -17162,6 +17207,7 @@
     <row r="1046" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1046" s="2"/>
       <c r="I1046" s="1"/>
+      <c r="J1046" s="2"/>
       <c r="K1046" s="1"/>
     </row>
     <row r="1047" spans="8:11" x14ac:dyDescent="0.3">
@@ -17179,6 +17225,7 @@
     <row r="1049" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1049" s="2"/>
       <c r="I1049" s="1"/>
+      <c r="J1049" s="2"/>
       <c r="K1049" s="1"/>
     </row>
     <row r="1050" spans="8:11" x14ac:dyDescent="0.3">
@@ -17256,6 +17303,7 @@
     <row r="1062" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1062" s="2"/>
       <c r="I1062" s="1"/>
+      <c r="J1062" s="2"/>
       <c r="K1062" s="1"/>
     </row>
     <row r="1063" spans="8:11" x14ac:dyDescent="0.3">
@@ -17285,6 +17333,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -17296,16 +17345,19 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1070" s="2"/>
       <c r="I1070" s="1"/>
+      <c r="J1070" s="2"/>
       <c r="K1070" s="1"/>
     </row>
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -17317,16 +17369,19 @@
     <row r="1073" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1073" s="2"/>
       <c r="I1073" s="1"/>
+      <c r="J1073" s="2"/>
       <c r="K1073" s="1"/>
     </row>
     <row r="1074" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1074" s="2"/>
       <c r="I1074" s="1"/>
+      <c r="J1074" s="2"/>
       <c r="K1074" s="1"/>
     </row>
     <row r="1075" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1075" s="2"/>
       <c r="I1075" s="1"/>
+      <c r="J1075" s="2"/>
       <c r="K1075" s="1"/>
     </row>
     <row r="1076" spans="8:11" x14ac:dyDescent="0.3">
@@ -17338,11 +17393,13 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1078" s="2"/>
       <c r="I1078" s="1"/>
+      <c r="J1078" s="2"/>
       <c r="K1078" s="1"/>
     </row>
     <row r="1079" spans="8:11" x14ac:dyDescent="0.3">
@@ -17366,6 +17423,7 @@
     <row r="1082" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1082" s="2"/>
       <c r="I1082" s="1"/>
+      <c r="J1082" s="2"/>
       <c r="K1082" s="1"/>
     </row>
     <row r="1083" spans="8:11" x14ac:dyDescent="0.3">
@@ -17407,6 +17465,7 @@
     <row r="1089" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1089" s="2"/>
       <c r="I1089" s="1"/>
+      <c r="J1089" s="2"/>
       <c r="K1089" s="1"/>
     </row>
     <row r="1090" spans="8:11" x14ac:dyDescent="0.3">
@@ -17436,21 +17495,25 @@
     <row r="1094" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1094" s="2"/>
       <c r="I1094" s="1"/>
+      <c r="J1094" s="2"/>
       <c r="K1094" s="1"/>
     </row>
     <row r="1095" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1095" s="2"/>
       <c r="I1095" s="1"/>
+      <c r="J1095" s="2"/>
       <c r="K1095" s="1"/>
     </row>
     <row r="1096" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1096" s="2"/>
       <c r="I1096" s="1"/>
+      <c r="J1096" s="2"/>
       <c r="K1096" s="1"/>
     </row>
     <row r="1097" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1097" s="2"/>
       <c r="I1097" s="1"/>
+      <c r="J1097" s="2"/>
       <c r="K1097" s="1"/>
     </row>
     <row r="1098" spans="8:11" x14ac:dyDescent="0.3">
@@ -17462,6 +17525,7 @@
     <row r="1099" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
+      <c r="J1099" s="2"/>
       <c r="K1099" s="1"/>
     </row>
     <row r="1100" spans="8:11" x14ac:dyDescent="0.3">
@@ -17479,6 +17543,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -17518,11 +17583,13 @@
     <row r="1109" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1109" s="2"/>
       <c r="I1109" s="1"/>
+      <c r="J1109" s="2"/>
       <c r="K1109" s="1"/>
     </row>
     <row r="1110" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1110" s="2"/>
       <c r="I1110" s="1"/>
+      <c r="J1110" s="2"/>
       <c r="K1110" s="1"/>
     </row>
     <row r="1111" spans="8:11" x14ac:dyDescent="0.3">
@@ -17570,6 +17637,7 @@
     <row r="1118" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1118" s="2"/>
       <c r="I1118" s="1"/>
+      <c r="J1118" s="2"/>
       <c r="K1118" s="1"/>
     </row>
     <row r="1119" spans="8:11" x14ac:dyDescent="0.3">
@@ -17599,6 +17667,7 @@
     <row r="1123" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1123" s="2"/>
       <c r="I1123" s="1"/>
+      <c r="J1123" s="2"/>
       <c r="K1123" s="1"/>
     </row>
     <row r="1124" spans="8:11" x14ac:dyDescent="0.3">
@@ -17675,6 +17744,7 @@
     <row r="1136" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1136" s="2"/>
       <c r="I1136" s="1"/>
+      <c r="J1136" s="2"/>
       <c r="K1136" s="1"/>
     </row>
     <row r="1137" spans="8:11" x14ac:dyDescent="0.3">
@@ -17721,6 +17791,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -17756,11 +17827,13 @@
     <row r="1150" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1150" s="2"/>
       <c r="I1150" s="1"/>
+      <c r="J1150" s="2"/>
       <c r="K1150" s="1"/>
     </row>
     <row r="1151" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1151" s="2"/>
       <c r="I1151" s="1"/>
+      <c r="J1151" s="2"/>
       <c r="K1151" s="1"/>
     </row>
     <row r="1152" spans="8:11" x14ac:dyDescent="0.3">
@@ -17777,6 +17850,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -17787,6 +17861,7 @@
     <row r="1156" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1156" s="2"/>
       <c r="I1156" s="1"/>
+      <c r="J1156" s="2"/>
       <c r="K1156" s="1"/>
     </row>
     <row r="1157" spans="8:11" x14ac:dyDescent="0.3">
@@ -17822,6 +17897,7 @@
     <row r="1162" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1162" s="2"/>
       <c r="I1162" s="1"/>
+      <c r="J1162" s="2"/>
       <c r="K1162" s="1"/>
     </row>
     <row r="1163" spans="8:11" x14ac:dyDescent="0.3">
@@ -17833,6 +17909,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -17844,6 +17921,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -17855,6 +17933,7 @@
     <row r="1168" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1168" s="2"/>
       <c r="I1168" s="1"/>
+      <c r="J1168" s="2"/>
       <c r="K1168" s="1"/>
     </row>
     <row r="1169" spans="8:11" x14ac:dyDescent="0.3">
@@ -17866,6 +17945,7 @@
     <row r="1170" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1170" s="2"/>
       <c r="I1170" s="1"/>
+      <c r="J1170" s="2"/>
       <c r="K1170" s="1"/>
     </row>
     <row r="1171" spans="8:11" x14ac:dyDescent="0.3">
@@ -17907,6 +17987,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -17924,6 +18005,7 @@
     <row r="1180" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1180" s="2"/>
       <c r="I1180" s="1"/>
+      <c r="J1180" s="2"/>
       <c r="K1180" s="1"/>
     </row>
     <row r="1181" spans="8:11" x14ac:dyDescent="0.3">
@@ -17941,6 +18023,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -17982,6 +18065,7 @@
     <row r="1190" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1190" s="2"/>
       <c r="I1190" s="1"/>
+      <c r="J1190" s="2"/>
       <c r="K1190" s="1"/>
     </row>
     <row r="1191" spans="8:11" x14ac:dyDescent="0.3">
@@ -18005,6 +18089,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -18051,6 +18136,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -18086,6 +18172,7 @@
     <row r="1208" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1208" s="2"/>
       <c r="I1208" s="1"/>
+      <c r="J1208" s="2"/>
       <c r="K1208" s="1"/>
     </row>
     <row r="1209" spans="8:11" x14ac:dyDescent="0.3">
@@ -18109,6 +18196,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -18149,6 +18237,7 @@
     <row r="1219" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1219" s="2"/>
       <c r="I1219" s="1"/>
+      <c r="J1219" s="2"/>
       <c r="K1219" s="1"/>
     </row>
     <row r="1220" spans="8:11" x14ac:dyDescent="0.3">
@@ -18166,11 +18255,13 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1223" s="2"/>
       <c r="I1223" s="1"/>
+      <c r="J1223" s="2"/>
       <c r="K1223" s="1"/>
     </row>
     <row r="1224" spans="8:11" x14ac:dyDescent="0.3">
@@ -18229,6 +18320,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -18245,6 +18337,7 @@
     <row r="1236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1236" s="2"/>
       <c r="I1236" s="1"/>
+      <c r="J1236" s="2"/>
       <c r="K1236" s="1"/>
     </row>
     <row r="1237" spans="8:11" x14ac:dyDescent="0.3">
@@ -18256,6 +18349,7 @@
     <row r="1238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1238" s="2"/>
       <c r="I1238" s="1"/>
+      <c r="J1238" s="2"/>
       <c r="K1238" s="1"/>
     </row>
     <row r="1239" spans="8:11" x14ac:dyDescent="0.3">
@@ -18267,11 +18361,13 @@
     <row r="1240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1240" s="2"/>
       <c r="I1240" s="1"/>
+      <c r="J1240" s="2"/>
       <c r="K1240" s="1"/>
     </row>
     <row r="1241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1241" s="2"/>
       <c r="I1241" s="1"/>
+      <c r="J1241" s="2"/>
       <c r="K1241" s="1"/>
     </row>
     <row r="1242" spans="8:11" x14ac:dyDescent="0.3">
@@ -18307,6 +18403,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -18359,6 +18456,7 @@
     <row r="1256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
+      <c r="J1256" s="2"/>
       <c r="K1256" s="1"/>
     </row>
     <row r="1257" spans="8:11" x14ac:dyDescent="0.3">
@@ -18369,6 +18467,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -18384,6 +18483,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -18407,16 +18507,19 @@
     <row r="1265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1265" s="2"/>
       <c r="I1265" s="1"/>
+      <c r="J1265" s="2"/>
       <c r="K1265" s="1"/>
     </row>
     <row r="1266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1266" s="2"/>
       <c r="I1266" s="1"/>
+      <c r="J1266" s="2"/>
       <c r="K1266" s="1"/>
     </row>
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -18487,6 +18590,7 @@
     <row r="1279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1279" s="2"/>
       <c r="I1279" s="1"/>
+      <c r="J1279" s="2"/>
       <c r="K1279" s="1"/>
     </row>
     <row r="1280" spans="8:11" x14ac:dyDescent="0.3">
@@ -18498,6 +18602,7 @@
     <row r="1281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1281" s="2"/>
       <c r="I1281" s="1"/>
+      <c r="J1281" s="2"/>
       <c r="K1281" s="1"/>
     </row>
     <row r="1282" spans="8:11" x14ac:dyDescent="0.3">
@@ -18598,6 +18703,8 @@
     <row r="1298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1298" s="2"/>
       <c r="I1298" s="1"/>
+      <c r="J1298" s="2"/>
+      <c r="K1298" s="1"/>
     </row>
     <row r="1299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1299" s="2"/>
@@ -18654,6 +18761,7 @@
     <row r="1308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1308" s="2"/>
       <c r="I1308" s="1"/>
+      <c r="J1308" s="2"/>
       <c r="K1308" s="1"/>
     </row>
     <row r="1309" spans="8:11" x14ac:dyDescent="0.3">
@@ -18677,6 +18785,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -18801,6 +18910,7 @@
     <row r="1333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1333" s="2"/>
       <c r="I1333" s="1"/>
+      <c r="J1333" s="2"/>
       <c r="K1333" s="1"/>
     </row>
     <row r="1334" spans="8:11" x14ac:dyDescent="0.3">
@@ -18959,6 +19069,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -18976,6 +19087,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -19016,6 +19128,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -19348,6 +19461,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -19436,6 +19550,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -19529,6 +19644,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -19588,11 +19704,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -19644,6 +19762,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -19685,6 +19804,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -19729,6 +19849,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -19775,11 +19896,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -19977,6 +20100,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -20006,6 +20130,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -20021,6 +20147,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -20080,6 +20207,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -20151,6 +20279,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -20192,6 +20321,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -20310,6 +20440,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -20374,6 +20505,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -20498,6 +20630,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -20724,6 +20857,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -20841,6 +20975,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -20924,6 +21059,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -20983,6 +21119,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -21006,6 +21143,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -21053,6 +21191,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -21112,6 +21251,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -21135,6 +21275,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -21152,6 +21293,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -21235,6 +21377,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -21426,6 +21569,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -49282,6 +49426,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -49289,6 +49434,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -49296,6 +49442,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -49311,6 +49458,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -49320,6 +49468,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -49327,9 +49476,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -49337,12 +49492,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -49350,12 +49508,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -49367,9 +49528,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -49384,6 +49547,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -49410,6 +49574,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -49420,7 +49585,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -49428,6 +49598,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -49439,6 +49610,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -49446,6 +49618,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -49460,13 +49633,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -49477,15 +49656,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -49501,6 +49683,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -49519,6 +49702,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -49530,6 +49714,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -49547,18 +49732,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -49587,6 +49777,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -49594,9 +49785,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -49619,12 +49812,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -49639,9 +49835,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -49657,12 +49855,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -49683,6 +49883,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -49694,9 +49895,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -49708,6 +49911,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -49747,9 +49951,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -49757,9 +49963,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -49770,6 +49978,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -49777,18 +49986,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -49796,6 +50013,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -49806,6 +50024,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -49832,15 +50051,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -49862,6 +50085,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -49869,9 +50093,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -49879,6 +50105,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -49890,6 +50117,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -49904,6 +50132,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -49913,6 +50145,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -49924,6 +50157,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -49934,10 +50168,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -49945,6 +50184,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -49959,6 +50199,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -49981,6 +50222,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -50000,25 +50242,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -50026,6 +50280,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -50033,15 +50288,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -50055,6 +50317,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -50073,9 +50336,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -50083,9 +50348,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -50093,6 +50360,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -50109,10 +50377,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
